--- a/sample_data/coverage_master.xlsx
+++ b/sample_data/coverage_master.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1959" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1935" uniqueCount="620">
   <si>
     <t>담보코드</t>
   </si>
@@ -845,15 +845,6 @@
     <t>TK0234</t>
   </si>
   <si>
-    <t>TK0235</t>
-  </si>
-  <si>
-    <t>TK0236</t>
-  </si>
-  <si>
-    <t>TK0237</t>
-  </si>
-  <si>
     <t>TK8001</t>
   </si>
   <si>
@@ -1409,19 +1400,16 @@
     <t>R(무)림프절전이암진단특약(갱신형)(간편심사형)</t>
   </si>
   <si>
-    <t>R(무)소액암진단특약(갱신형)(간편심사형)</t>
+    <t>R(무)암산정특례대상보장특약(갱신형)(간편심사형)</t>
   </si>
   <si>
     <t>R(무)암수술특약(갱신형)(간편심사형)</t>
   </si>
   <si>
-    <t>R(무)암직접치료(요양병원제외)입원특약(갱신형)(간편심사형)</t>
-  </si>
-  <si>
     <t>R(무)암직접치료상급종합병원통원특약(연간30회)(갱신형)(간편심사형)</t>
   </si>
   <si>
-    <t>R(무)암직접치료종합병원통원특약(연간30회)(갱신형)(간편심사형)</t>
+    <t>R(무)암직접치료상급종합병원통원특약Ⅱ(갱신형)(간편심사형)</t>
   </si>
   <si>
     <t>R(무)암직접치료통원특약(갱신형)(간편심사형)</t>
@@ -1436,19 +1424,16 @@
     <t>R(무)항암방사선치료특약(갱신형)(간편심사형)</t>
   </si>
   <si>
-    <t>R(무)항암약물치료특약(갱신형)(간편심사형)</t>
+    <t>R(무)항암중입자방사선치료특약(갱신형)(간편심사형)</t>
   </si>
   <si>
     <t>R(무)관상동맥(심장동맥)우회수술특약(갱신형)(간편심사형)</t>
   </si>
   <si>
-    <t>R(무)급성뇌경색증혈전용해치료특약(갱신형)(간편심사형)</t>
-  </si>
-  <si>
     <t>R(무)급성심근경색증진단특약(갱신형)(간편심사형)</t>
   </si>
   <si>
-    <t>R(무)뇌졸중진단특약(갱신형)(간편심사형)</t>
+    <t>R(무)급성심근경색증혈전용해치료특약(갱신형)(간편심사형)</t>
   </si>
   <si>
     <t>R(무)뇌출혈진단특약(갱신형)(간편심사형)</t>
@@ -1463,19 +1448,16 @@
     <t>R(무)뇌혈관질환입원특약(갱신형)(간편심사형)</t>
   </si>
   <si>
-    <t>R(무)뇌혈관질환종합병원통원특약(연간30회)(갱신형)(간편심사형)</t>
+    <t>R(무)뇌혈관질환진단특약(갱신형)(간편심사형)</t>
   </si>
   <si>
     <t>R(무)뇌혈관질환통원특약(연간30회)(갱신형)(간편심사형)</t>
   </si>
   <si>
-    <t>R(무)부정맥진단특약(갱신형)(간편심사형)</t>
-  </si>
-  <si>
     <t>R(무)심장질환산정특례대상보장특약(갱신형)(간편심사형)</t>
   </si>
   <si>
-    <t>R(무)허혈성심장질환상급종합병원통원특약(연간30회)(갱신형)(간편심사형)</t>
+    <t>R(무)심장판막수술특약(갱신형)(간편심사형)</t>
   </si>
   <si>
     <t>R(무)허혈성심장질환수술특약(갱신형)(간편심사형)</t>
@@ -1490,19 +1472,16 @@
     <t>R(무)허혈성심장질환통원특약(연간30회)(갱신형)(간편심사형)</t>
   </si>
   <si>
-    <t>R(무)1~5종수술특약(갱신형)(간편심사형)</t>
+    <t>R(무)3대기관양성신생물및용종수술특약(갱신형)(간편심사형)</t>
   </si>
   <si>
     <t>R(무)6대질병장해(50%이상)보장특약(갱신형)(간편심사형)</t>
   </si>
   <si>
-    <t>R(무)갑상선기능항진증치료특약(갱신형)(간편심사형)</t>
-  </si>
-  <si>
     <t>R(무)깁스치료특약(갱신형)(간편심사형)</t>
   </si>
   <si>
-    <t>R(무)입원간병인사용(요양병원)특약(갱신형)(간편심사형)</t>
+    <t>R(무)응급실내원특약(갱신형)(간편심사형)</t>
   </si>
   <si>
     <t>R(무)입원간병인사용(요양병원제외)특약(갱신형)(간편심사형)</t>
@@ -1517,7 +1496,7 @@
     <t>R(무)재해수술특약(갱신형)(간편심사형)</t>
   </si>
   <si>
-    <t>R(무)재해장해(3~100%)보장특약(갱신형)(간편심사형)</t>
+    <t>R(무)재해장해(50%이상)보장특약(갱신형)(간편심사형)</t>
   </si>
   <si>
     <t>R(무)재해장해(80%이상)보장특약(갱신형)(간편심사형)</t>
@@ -1526,13 +1505,10 @@
     <t>R(무)조혈모세포이식수술특약(갱신형)(간편심사형)</t>
   </si>
   <si>
-    <t>R(무)질병장해(3~100%)보장특약(갱신형)(간편심사형)</t>
-  </si>
-  <si>
     <t>R(무)질병장해(50%이상)보장특약(갱신형)(간편심사형)</t>
   </si>
   <si>
-    <t>R(무)첫날부터상급종합병원입원(1~120일)특약(갱신형)(간편심사형)</t>
+    <t>R(무)질병장해(80%이상)보장특약(갱신형)(간편심사형)</t>
   </si>
   <si>
     <t>R(무)첫날부터상급종합병원입원(1~30일)특약(갱신형)(간편심사형)</t>
@@ -1541,6 +1517,9 @@
     <t>R(무)첫날부터입원(1~120일)특약(갱신형)(간편심사형)</t>
   </si>
   <si>
+    <t>R(무)첫날부터입원(1~30일)특약(갱신형)(간편심사형)</t>
+  </si>
+  <si>
     <t>R(무)첫날부터종합병원입원(1~30일)특약(갱신형)(간편심사형)</t>
   </si>
   <si>
@@ -1548,6 +1527,9 @@
   </si>
   <si>
     <t>R(무)3대주요암진단특약(갱신형)(간편심사형)</t>
+  </si>
+  <si>
+    <t>R(무)상급종합병원질병수술(백내장 및 대장용종 제외)특약(갱신형)(간편심사형)</t>
   </si>
   <si>
     <t>R(무)종합병원질병수술(백내장 및 대장용종 제외)특약(갱신형)(간편심사형)</t>
@@ -2224,7 +2206,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H243"/>
+  <dimension ref="A1:H240"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -2264,19 +2246,19 @@
         <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E2" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F2" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G2" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="H2" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2290,19 +2272,19 @@
         <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E3" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F3" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G3" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="H3" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -2316,19 +2298,19 @@
         <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="E4" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F4" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G4" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="H4" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2342,19 +2324,19 @@
         <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E5" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F5" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G5" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="H5" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2368,19 +2350,19 @@
         <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="E6" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F6" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G6" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="H6" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -2394,19 +2376,19 @@
         <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="E7" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F7" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G7" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="H7" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -2420,19 +2402,19 @@
         <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E8" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F8" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G8" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="H8" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -2446,19 +2428,19 @@
         <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E9" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F9" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G9" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="H9" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -2472,19 +2454,19 @@
         <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E10" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F10" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G10" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="H10" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -2498,19 +2480,19 @@
         <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E11" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F11" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G11" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="H11" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -2524,19 +2506,19 @@
         <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="E12" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F12" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G12" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H12" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -2550,19 +2532,19 @@
         <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E13" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F13" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G13" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H13" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -2576,19 +2558,19 @@
         <v>54</v>
       </c>
       <c r="D14" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E14" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F14" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G14" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="H14" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -2602,19 +2584,19 @@
         <v>55</v>
       </c>
       <c r="D15" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="E15" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F15" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G15" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H15" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -2628,19 +2610,19 @@
         <v>56</v>
       </c>
       <c r="D16" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="E16" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F16" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G16" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="H16" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -2654,19 +2636,19 @@
         <v>57</v>
       </c>
       <c r="D17" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E17" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F17" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G17" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="H17" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -2680,19 +2662,19 @@
         <v>58</v>
       </c>
       <c r="D18" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E18" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F18" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G18" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="H18" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -2706,19 +2688,19 @@
         <v>59</v>
       </c>
       <c r="D19" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E19" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F19" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G19" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="H19" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -2732,19 +2714,19 @@
         <v>60</v>
       </c>
       <c r="D20" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="E20" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F20" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G20" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="H20" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -2758,19 +2740,19 @@
         <v>61</v>
       </c>
       <c r="D21" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="E21" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F21" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G21" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="H21" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -2784,19 +2766,19 @@
         <v>62</v>
       </c>
       <c r="D22" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E22" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F22" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G22" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="H22" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -2810,19 +2792,19 @@
         <v>63</v>
       </c>
       <c r="D23" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E23" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F23" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G23" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="H23" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -2836,19 +2818,19 @@
         <v>64</v>
       </c>
       <c r="D24" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E24" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F24" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G24" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="H24" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -2862,19 +2844,19 @@
         <v>65</v>
       </c>
       <c r="D25" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="E25" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F25" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G25" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="H25" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -2888,19 +2870,19 @@
         <v>66</v>
       </c>
       <c r="D26" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="E26" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F26" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G26" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="H26" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -2914,19 +2896,19 @@
         <v>67</v>
       </c>
       <c r="D27" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="E27" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F27" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G27" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="H27" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -2940,19 +2922,19 @@
         <v>68</v>
       </c>
       <c r="D28" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="E28" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F28" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G28" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="H28" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -2966,19 +2948,19 @@
         <v>69</v>
       </c>
       <c r="D29" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="E29" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F29" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G29" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="H29" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -2992,19 +2974,19 @@
         <v>70</v>
       </c>
       <c r="D30" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="E30" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F30" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G30" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="H30" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -3018,19 +3000,19 @@
         <v>71</v>
       </c>
       <c r="D31" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E31" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F31" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G31" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="H31" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -3044,19 +3026,19 @@
         <v>72</v>
       </c>
       <c r="D32" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="E32" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F32" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G32" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H32" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -3070,19 +3052,19 @@
         <v>73</v>
       </c>
       <c r="D33" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="E33" t="s">
+        <v>520</v>
+      </c>
+      <c r="F33" t="s">
         <v>526</v>
       </c>
-      <c r="F33" t="s">
-        <v>532</v>
-      </c>
       <c r="G33" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="H33" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -3096,19 +3078,19 @@
         <v>74</v>
       </c>
       <c r="D34" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E34" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F34" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G34" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="H34" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -3122,19 +3104,19 @@
         <v>75</v>
       </c>
       <c r="D35" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="E35" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F35" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G35" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="H35" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -3148,19 +3130,19 @@
         <v>76</v>
       </c>
       <c r="D36" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="E36" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F36" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="G36" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="H36" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -3174,19 +3156,19 @@
         <v>77</v>
       </c>
       <c r="D37" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="E37" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F37" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="G37" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="H37" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -3200,19 +3182,19 @@
         <v>78</v>
       </c>
       <c r="D38" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E38" t="s">
+        <v>520</v>
+      </c>
+      <c r="F38" t="s">
         <v>526</v>
       </c>
-      <c r="F38" t="s">
-        <v>532</v>
-      </c>
       <c r="G38" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="H38" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -3226,19 +3208,19 @@
         <v>79</v>
       </c>
       <c r="D39" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="E39" t="s">
+        <v>520</v>
+      </c>
+      <c r="F39" t="s">
         <v>526</v>
       </c>
-      <c r="F39" t="s">
-        <v>532</v>
-      </c>
       <c r="G39" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="H39" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -3252,19 +3234,19 @@
         <v>80</v>
       </c>
       <c r="D40" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E40" t="s">
+        <v>520</v>
+      </c>
+      <c r="F40" t="s">
         <v>526</v>
       </c>
-      <c r="F40" t="s">
-        <v>532</v>
-      </c>
       <c r="G40" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="H40" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -3278,19 +3260,19 @@
         <v>81</v>
       </c>
       <c r="D41" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="E41" t="s">
+        <v>520</v>
+      </c>
+      <c r="F41" t="s">
         <v>526</v>
       </c>
-      <c r="F41" t="s">
-        <v>532</v>
-      </c>
       <c r="G41" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="H41" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -3304,19 +3286,19 @@
         <v>82</v>
       </c>
       <c r="D42" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E42" t="s">
+        <v>520</v>
+      </c>
+      <c r="F42" t="s">
         <v>526</v>
       </c>
-      <c r="F42" t="s">
-        <v>532</v>
-      </c>
       <c r="G42" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H42" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -3330,19 +3312,19 @@
         <v>83</v>
       </c>
       <c r="D43" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E43" t="s">
+        <v>520</v>
+      </c>
+      <c r="F43" t="s">
         <v>526</v>
       </c>
-      <c r="F43" t="s">
-        <v>532</v>
-      </c>
       <c r="G43" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="H43" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -3356,19 +3338,19 @@
         <v>84</v>
       </c>
       <c r="D44" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="E44" t="s">
+        <v>520</v>
+      </c>
+      <c r="F44" t="s">
         <v>526</v>
       </c>
-      <c r="F44" t="s">
-        <v>532</v>
-      </c>
       <c r="G44" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="H44" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -3382,19 +3364,19 @@
         <v>85</v>
       </c>
       <c r="D45" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="E45" t="s">
+        <v>520</v>
+      </c>
+      <c r="F45" t="s">
         <v>526</v>
       </c>
-      <c r="F45" t="s">
-        <v>532</v>
-      </c>
       <c r="G45" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="H45" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -3408,19 +3390,19 @@
         <v>86</v>
       </c>
       <c r="D46" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="E46" t="s">
+        <v>520</v>
+      </c>
+      <c r="F46" t="s">
         <v>526</v>
       </c>
-      <c r="F46" t="s">
-        <v>532</v>
-      </c>
       <c r="G46" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="H46" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -3434,19 +3416,19 @@
         <v>87</v>
       </c>
       <c r="D47" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E47" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F47" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G47" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="H47" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -3460,19 +3442,19 @@
         <v>88</v>
       </c>
       <c r="D48" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E48" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F48" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G48" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="H48" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -3486,19 +3468,19 @@
         <v>89</v>
       </c>
       <c r="D49" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="E49" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F49" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G49" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H49" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -3512,19 +3494,19 @@
         <v>90</v>
       </c>
       <c r="D50" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="E50" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F50" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G50" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="H50" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -3538,19 +3520,19 @@
         <v>91</v>
       </c>
       <c r="D51" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="E51" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F51" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G51" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H51" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -3564,19 +3546,19 @@
         <v>92</v>
       </c>
       <c r="D52" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E52" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F52" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G52" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="H52" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -3590,19 +3572,19 @@
         <v>93</v>
       </c>
       <c r="D53" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E53" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F53" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G53" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="H53" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -3616,19 +3598,19 @@
         <v>94</v>
       </c>
       <c r="D54" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E54" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F54" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G54" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="H54" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -3642,19 +3624,19 @@
         <v>95</v>
       </c>
       <c r="D55" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E55" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F55" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G55" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="H55" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -3668,19 +3650,19 @@
         <v>96</v>
       </c>
       <c r="D56" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="E56" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F56" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="G56" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H56" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -3694,19 +3676,19 @@
         <v>97</v>
       </c>
       <c r="D57" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E57" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F57" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="G57" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H57" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -3720,19 +3702,19 @@
         <v>98</v>
       </c>
       <c r="D58" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E58" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F58" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="G58" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="H58" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -3746,19 +3728,19 @@
         <v>99</v>
       </c>
       <c r="D59" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="E59" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F59" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="G59" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="H59" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -3772,19 +3754,19 @@
         <v>100</v>
       </c>
       <c r="D60" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E60" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="F60" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="G60" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="H60" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -3798,19 +3780,19 @@
         <v>101</v>
       </c>
       <c r="D61" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="E61" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F61" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="G61" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="H61" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -3824,19 +3806,19 @@
         <v>102</v>
       </c>
       <c r="D62" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="E62" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F62" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="G62" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="H62" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -3850,19 +3832,19 @@
         <v>103</v>
       </c>
       <c r="D63" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="E63" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F63" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="G63" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="H63" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -3876,19 +3858,19 @@
         <v>104</v>
       </c>
       <c r="D64" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="E64" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F64" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="G64" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="H64" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -3902,19 +3884,19 @@
         <v>105</v>
       </c>
       <c r="D65" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="E65" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="F65" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="G65" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="H65" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -3928,19 +3910,19 @@
         <v>106</v>
       </c>
       <c r="D66" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E66" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="F66" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="G66" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="H66" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -3954,19 +3936,19 @@
         <v>107</v>
       </c>
       <c r="D67" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="E67" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="F67" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="G67" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H67" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -3980,19 +3962,19 @@
         <v>108</v>
       </c>
       <c r="D68" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E68" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="F68" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="G68" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="H68" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -4006,19 +3988,19 @@
         <v>109</v>
       </c>
       <c r="D69" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="E69" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="F69" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="G69" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="H69" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -4032,19 +4014,19 @@
         <v>110</v>
       </c>
       <c r="D70" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E70" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="F70" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="G70" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="H70" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -4058,19 +4040,19 @@
         <v>111</v>
       </c>
       <c r="D71" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E71" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="F71" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="G71" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="H71" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -4084,19 +4066,19 @@
         <v>112</v>
       </c>
       <c r="D72" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E72" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="F72" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="G72" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="H72" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -4110,19 +4092,19 @@
         <v>113</v>
       </c>
       <c r="D73" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="E73" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F73" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="G73" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="H73" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -4136,19 +4118,19 @@
         <v>114</v>
       </c>
       <c r="D74" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E74" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F74" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="G74" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="H74" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -4162,19 +4144,19 @@
         <v>115</v>
       </c>
       <c r="D75" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="E75" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F75" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="G75" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="H75" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -4188,19 +4170,19 @@
         <v>116</v>
       </c>
       <c r="D76" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="E76" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F76" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="G76" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="H76" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -4214,19 +4196,19 @@
         <v>117</v>
       </c>
       <c r="D77" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="E77" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F77" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="G77" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="H77" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -4240,19 +4222,19 @@
         <v>118</v>
       </c>
       <c r="D78" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E78" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F78" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="G78" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="H78" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -4266,19 +4248,19 @@
         <v>119</v>
       </c>
       <c r="D79" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="E79" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F79" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="G79" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="H79" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -4292,19 +4274,19 @@
         <v>120</v>
       </c>
       <c r="D80" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E80" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F80" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="G80" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="H80" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -4318,19 +4300,19 @@
         <v>121</v>
       </c>
       <c r="D81" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="E81" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F81" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="G81" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="H81" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -4344,19 +4326,19 @@
         <v>122</v>
       </c>
       <c r="D82" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="E82" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F82" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G82" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="H82" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -4370,19 +4352,19 @@
         <v>123</v>
       </c>
       <c r="D83" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="E83" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F83" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="G83" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H83" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -4396,19 +4378,19 @@
         <v>124</v>
       </c>
       <c r="D84" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E84" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F84" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="G84" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H84" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -4422,19 +4404,19 @@
         <v>125</v>
       </c>
       <c r="D85" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E85" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F85" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="G85" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H85" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -4448,19 +4430,19 @@
         <v>126</v>
       </c>
       <c r="D86" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="E86" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F86" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="G86" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H86" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -4474,19 +4456,19 @@
         <v>127</v>
       </c>
       <c r="D87" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E87" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F87" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="G87" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H87" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -4500,19 +4482,19 @@
         <v>128</v>
       </c>
       <c r="D88" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E88" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F88" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G88" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="H88" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -4526,19 +4508,19 @@
         <v>129</v>
       </c>
       <c r="D89" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E89" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F89" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G89" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="H89" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -4552,19 +4534,19 @@
         <v>130</v>
       </c>
       <c r="D90" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E90" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F90" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G90" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="H90" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -4578,19 +4560,19 @@
         <v>131</v>
       </c>
       <c r="D91" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E91" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F91" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G91" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="H91" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -4604,19 +4586,19 @@
         <v>132</v>
       </c>
       <c r="D92" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="E92" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F92" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="G92" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="H92" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -4630,19 +4612,19 @@
         <v>133</v>
       </c>
       <c r="D93" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="E93" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F93" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="G93" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="H93" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -4656,19 +4638,19 @@
         <v>134</v>
       </c>
       <c r="D94" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="E94" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="F94" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="G94" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="H94" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -4682,19 +4664,19 @@
         <v>135</v>
       </c>
       <c r="D95" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="E95" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="F95" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="G95" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="H95" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -4708,19 +4690,19 @@
         <v>136</v>
       </c>
       <c r="D96" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E96" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="F96" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="G96" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="H96" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -4734,19 +4716,19 @@
         <v>137</v>
       </c>
       <c r="D97" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E97" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="F97" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="G97" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="H97" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -4760,19 +4742,19 @@
         <v>138</v>
       </c>
       <c r="D98" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E98" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="F98" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="G98" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="H98" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -4786,19 +4768,19 @@
         <v>139</v>
       </c>
       <c r="D99" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E99" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="F99" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="G99" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="H99" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -4812,19 +4794,19 @@
         <v>140</v>
       </c>
       <c r="D100" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E100" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="F100" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="G100" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="H100" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -4838,19 +4820,19 @@
         <v>141</v>
       </c>
       <c r="D101" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E101" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="F101" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="G101" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="H101" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -4864,19 +4846,19 @@
         <v>142</v>
       </c>
       <c r="D102" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E102" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="F102" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="G102" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="H102" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -4890,19 +4872,19 @@
         <v>143</v>
       </c>
       <c r="D103" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="E103" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="F103" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="G103" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="H103" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -4916,19 +4898,19 @@
         <v>144</v>
       </c>
       <c r="D104" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="E104" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F104" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G104" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="H104" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -4942,19 +4924,19 @@
         <v>145</v>
       </c>
       <c r="D105" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E105" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F105" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G105" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="H105" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -4968,19 +4950,19 @@
         <v>146</v>
       </c>
       <c r="D106" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="E106" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F106" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G106" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="H106" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -4994,19 +4976,19 @@
         <v>147</v>
       </c>
       <c r="D107" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E107" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F107" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G107" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="H107" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -5020,19 +5002,19 @@
         <v>148</v>
       </c>
       <c r="D108" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="E108" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F108" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G108" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="H108" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -5046,19 +5028,19 @@
         <v>149</v>
       </c>
       <c r="D109" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E109" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F109" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G109" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H109" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -5072,19 +5054,19 @@
         <v>150</v>
       </c>
       <c r="D110" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="E110" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F110" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G110" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="H110" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -5098,19 +5080,19 @@
         <v>151</v>
       </c>
       <c r="D111" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E111" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F111" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G111" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="H111" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -5124,19 +5106,19 @@
         <v>152</v>
       </c>
       <c r="D112" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="E112" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F112" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G112" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="H112" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -5150,19 +5132,19 @@
         <v>153</v>
       </c>
       <c r="D113" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="E113" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F113" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G113" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="H113" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -5176,19 +5158,19 @@
         <v>154</v>
       </c>
       <c r="D114" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E114" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F114" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G114" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="H114" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -5202,19 +5184,19 @@
         <v>155</v>
       </c>
       <c r="D115" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="E115" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F115" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G115" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="H115" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -5228,19 +5210,19 @@
         <v>156</v>
       </c>
       <c r="D116" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E116" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F116" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G116" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="H116" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -5254,19 +5236,19 @@
         <v>157</v>
       </c>
       <c r="D117" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E117" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F117" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G117" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="H117" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -5280,19 +5262,19 @@
         <v>158</v>
       </c>
       <c r="D118" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="E118" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F118" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G118" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="H118" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -5306,19 +5288,19 @@
         <v>159</v>
       </c>
       <c r="D119" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="E119" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F119" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G119" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="H119" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -5332,19 +5314,19 @@
         <v>160</v>
       </c>
       <c r="D120" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="E120" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F120" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G120" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="H120" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -5358,19 +5340,19 @@
         <v>161</v>
       </c>
       <c r="D121" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="E121" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F121" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G121" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H121" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -5384,19 +5366,19 @@
         <v>162</v>
       </c>
       <c r="D122" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E122" t="s">
+        <v>520</v>
+      </c>
+      <c r="F122" t="s">
         <v>526</v>
       </c>
-      <c r="F122" t="s">
-        <v>532</v>
-      </c>
       <c r="G122" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="H122" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -5410,19 +5392,19 @@
         <v>163</v>
       </c>
       <c r="D123" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E123" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F123" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G123" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="H123" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -5436,19 +5418,19 @@
         <v>164</v>
       </c>
       <c r="D124" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="E124" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F124" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G124" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="H124" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -5462,19 +5444,19 @@
         <v>165</v>
       </c>
       <c r="D125" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E125" t="s">
+        <v>520</v>
+      </c>
+      <c r="F125" t="s">
         <v>526</v>
       </c>
-      <c r="F125" t="s">
-        <v>532</v>
-      </c>
       <c r="G125" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="H125" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -5488,19 +5470,19 @@
         <v>166</v>
       </c>
       <c r="D126" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E126" t="s">
+        <v>520</v>
+      </c>
+      <c r="F126" t="s">
         <v>526</v>
       </c>
-      <c r="F126" t="s">
-        <v>532</v>
-      </c>
       <c r="G126" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="H126" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -5514,19 +5496,19 @@
         <v>167</v>
       </c>
       <c r="D127" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="E127" t="s">
+        <v>520</v>
+      </c>
+      <c r="F127" t="s">
         <v>526</v>
       </c>
-      <c r="F127" t="s">
-        <v>532</v>
-      </c>
       <c r="G127" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="H127" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -5540,19 +5522,19 @@
         <v>168</v>
       </c>
       <c r="D128" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="E128" t="s">
+        <v>520</v>
+      </c>
+      <c r="F128" t="s">
         <v>526</v>
       </c>
-      <c r="F128" t="s">
-        <v>532</v>
-      </c>
       <c r="G128" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="H128" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -5566,19 +5548,19 @@
         <v>169</v>
       </c>
       <c r="D129" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="E129" t="s">
+        <v>520</v>
+      </c>
+      <c r="F129" t="s">
         <v>526</v>
       </c>
-      <c r="F129" t="s">
-        <v>532</v>
-      </c>
       <c r="G129" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H129" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -5592,19 +5574,19 @@
         <v>170</v>
       </c>
       <c r="D130" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="E130" t="s">
+        <v>520</v>
+      </c>
+      <c r="F130" t="s">
         <v>526</v>
       </c>
-      <c r="F130" t="s">
-        <v>532</v>
-      </c>
       <c r="G130" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="H130" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -5618,19 +5600,19 @@
         <v>171</v>
       </c>
       <c r="D131" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="E131" t="s">
+        <v>520</v>
+      </c>
+      <c r="F131" t="s">
         <v>526</v>
       </c>
-      <c r="F131" t="s">
-        <v>532</v>
-      </c>
       <c r="G131" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="H131" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -5644,19 +5626,19 @@
         <v>172</v>
       </c>
       <c r="D132" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E132" t="s">
+        <v>520</v>
+      </c>
+      <c r="F132" t="s">
         <v>526</v>
       </c>
-      <c r="F132" t="s">
-        <v>532</v>
-      </c>
       <c r="G132" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="H132" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -5670,19 +5652,19 @@
         <v>173</v>
       </c>
       <c r="D133" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="E133" t="s">
+        <v>520</v>
+      </c>
+      <c r="F133" t="s">
         <v>526</v>
       </c>
-      <c r="F133" t="s">
-        <v>532</v>
-      </c>
       <c r="G133" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="H133" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -5696,19 +5678,19 @@
         <v>174</v>
       </c>
       <c r="D134" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="E134" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F134" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G134" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="H134" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
     </row>
     <row r="135" spans="1:8">
@@ -5722,19 +5704,19 @@
         <v>175</v>
       </c>
       <c r="D135" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="E135" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F135" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G135" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="H135" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
     </row>
     <row r="136" spans="1:8">
@@ -5748,19 +5730,19 @@
         <v>176</v>
       </c>
       <c r="D136" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="E136" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F136" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G136" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H136" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -5774,19 +5756,19 @@
         <v>177</v>
       </c>
       <c r="D137" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="E137" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F137" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G137" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="H137" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -5800,19 +5782,19 @@
         <v>178</v>
       </c>
       <c r="D138" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E138" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F138" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G138" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H138" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -5826,19 +5808,19 @@
         <v>179</v>
       </c>
       <c r="D139" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="E139" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F139" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G139" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="H139" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
     </row>
     <row r="140" spans="1:8">
@@ -5852,19 +5834,19 @@
         <v>180</v>
       </c>
       <c r="D140" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E140" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F140" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G140" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="H140" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -5878,19 +5860,19 @@
         <v>181</v>
       </c>
       <c r="D141" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="E141" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F141" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G141" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="H141" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
     </row>
     <row r="142" spans="1:8">
@@ -5904,19 +5886,19 @@
         <v>182</v>
       </c>
       <c r="D142" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="E142" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F142" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G142" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="H142" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
     </row>
     <row r="143" spans="1:8">
@@ -5930,19 +5912,19 @@
         <v>183</v>
       </c>
       <c r="D143" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="E143" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F143" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="G143" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H143" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
     </row>
     <row r="144" spans="1:8">
@@ -5956,19 +5938,19 @@
         <v>184</v>
       </c>
       <c r="D144" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E144" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F144" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="G144" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H144" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
     </row>
     <row r="145" spans="1:8">
@@ -5982,19 +5964,19 @@
         <v>185</v>
       </c>
       <c r="D145" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="E145" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F145" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="G145" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="H145" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -6008,19 +5990,19 @@
         <v>186</v>
       </c>
       <c r="D146" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E146" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F146" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="G146" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="H146" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
     </row>
     <row r="147" spans="1:8">
@@ -6034,19 +6016,19 @@
         <v>187</v>
       </c>
       <c r="D147" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E147" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="F147" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="G147" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="H147" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -6060,19 +6042,19 @@
         <v>188</v>
       </c>
       <c r="D148" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E148" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F148" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="G148" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="H148" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -6086,19 +6068,19 @@
         <v>189</v>
       </c>
       <c r="D149" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="E149" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F149" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="G149" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="H149" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -6112,19 +6094,19 @@
         <v>190</v>
       </c>
       <c r="D150" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="E150" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F150" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="G150" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="H150" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -6138,19 +6120,19 @@
         <v>191</v>
       </c>
       <c r="D151" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="E151" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F151" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="G151" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="H151" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -6164,19 +6146,19 @@
         <v>192</v>
       </c>
       <c r="D152" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E152" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="F152" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="G152" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="H152" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -6190,19 +6172,19 @@
         <v>193</v>
       </c>
       <c r="D153" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E153" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="F153" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="G153" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="H153" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -6216,19 +6198,19 @@
         <v>194</v>
       </c>
       <c r="D154" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E154" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="F154" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="G154" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H154" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -6242,19 +6224,19 @@
         <v>195</v>
       </c>
       <c r="D155" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="E155" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="F155" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="G155" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="H155" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -6268,19 +6250,19 @@
         <v>196</v>
       </c>
       <c r="D156" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E156" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="F156" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="G156" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="H156" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
     </row>
     <row r="157" spans="1:8">
@@ -6294,19 +6276,19 @@
         <v>197</v>
       </c>
       <c r="D157" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E157" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="F157" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="G157" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="H157" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -6320,19 +6302,19 @@
         <v>198</v>
       </c>
       <c r="D158" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E158" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F158" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="G158" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H158" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
     </row>
     <row r="159" spans="1:8">
@@ -6346,19 +6328,19 @@
         <v>199</v>
       </c>
       <c r="D159" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E159" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F159" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="G159" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="H159" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -6372,19 +6354,19 @@
         <v>200</v>
       </c>
       <c r="D160" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E160" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F160" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="G160" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="H160" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -6398,19 +6380,19 @@
         <v>201</v>
       </c>
       <c r="D161" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="E161" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F161" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="G161" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="H161" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
     </row>
     <row r="162" spans="1:8">
@@ -6424,19 +6406,19 @@
         <v>202</v>
       </c>
       <c r="D162" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E162" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F162" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="G162" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="H162" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
     </row>
     <row r="163" spans="1:8">
@@ -6450,19 +6432,19 @@
         <v>203</v>
       </c>
       <c r="D163" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E163" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F163" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="G163" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="H163" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
     </row>
     <row r="164" spans="1:8">
@@ -6476,19 +6458,19 @@
         <v>204</v>
       </c>
       <c r="D164" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E164" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F164" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="G164" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="H164" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
     </row>
     <row r="165" spans="1:8">
@@ -6502,19 +6484,19 @@
         <v>205</v>
       </c>
       <c r="D165" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="E165" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F165" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="G165" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="H165" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
     </row>
     <row r="166" spans="1:8">
@@ -6528,19 +6510,19 @@
         <v>206</v>
       </c>
       <c r="D166" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E166" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F166" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="G166" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="H166" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
     </row>
     <row r="167" spans="1:8">
@@ -6554,19 +6536,19 @@
         <v>207</v>
       </c>
       <c r="D167" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E167" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F167" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="G167" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="H167" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
     </row>
     <row r="168" spans="1:8">
@@ -6580,19 +6562,19 @@
         <v>208</v>
       </c>
       <c r="D168" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E168" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F168" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G168" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="H168" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
     </row>
     <row r="169" spans="1:8">
@@ -6606,19 +6588,19 @@
         <v>209</v>
       </c>
       <c r="D169" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="E169" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F169" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="G169" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H169" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
     </row>
     <row r="170" spans="1:8">
@@ -6632,19 +6614,19 @@
         <v>210</v>
       </c>
       <c r="D170" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E170" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F170" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="G170" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H170" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
     </row>
     <row r="171" spans="1:8">
@@ -6658,19 +6640,19 @@
         <v>211</v>
       </c>
       <c r="D171" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="E171" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F171" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="G171" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H171" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
     </row>
     <row r="172" spans="1:8">
@@ -6684,19 +6666,19 @@
         <v>212</v>
       </c>
       <c r="D172" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="E172" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F172" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="G172" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H172" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
     </row>
     <row r="173" spans="1:8">
@@ -6710,19 +6692,19 @@
         <v>213</v>
       </c>
       <c r="D173" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E173" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F173" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="G173" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H173" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
     </row>
     <row r="174" spans="1:8">
@@ -6736,19 +6718,19 @@
         <v>214</v>
       </c>
       <c r="D174" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E174" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F174" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G174" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="H174" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
     </row>
     <row r="175" spans="1:8">
@@ -6762,19 +6744,19 @@
         <v>215</v>
       </c>
       <c r="D175" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="E175" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F175" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G175" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="H175" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
     </row>
     <row r="176" spans="1:8">
@@ -6788,19 +6770,19 @@
         <v>216</v>
       </c>
       <c r="D176" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="E176" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F176" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G176" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="H176" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
     </row>
     <row r="177" spans="1:8">
@@ -6814,19 +6796,19 @@
         <v>217</v>
       </c>
       <c r="D177" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="E177" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F177" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G177" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="H177" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
     </row>
     <row r="178" spans="1:8">
@@ -6840,19 +6822,19 @@
         <v>218</v>
       </c>
       <c r="D178" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="E178" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F178" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="G178" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="H178" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -6866,19 +6848,19 @@
         <v>219</v>
       </c>
       <c r="D179" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="E179" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F179" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="G179" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="H179" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
     </row>
     <row r="180" spans="1:8">
@@ -6892,19 +6874,19 @@
         <v>220</v>
       </c>
       <c r="D180" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E180" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F180" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G180" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="H180" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -6918,19 +6900,19 @@
         <v>221</v>
       </c>
       <c r="D181" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E181" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F181" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G181" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="H181" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -6944,19 +6926,19 @@
         <v>222</v>
       </c>
       <c r="D182" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E182" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F182" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G182" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="H182" t="s">
-        <v>567</v>
+        <v>524</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -6970,19 +6952,19 @@
         <v>223</v>
       </c>
       <c r="D183" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E183" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F183" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G183" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H183" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -6996,19 +6978,19 @@
         <v>224</v>
       </c>
       <c r="D184" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E184" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F184" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G184" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H184" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
     </row>
     <row r="185" spans="1:8">
@@ -7022,19 +7004,19 @@
         <v>225</v>
       </c>
       <c r="D185" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="E185" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F185" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G185" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="H185" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
     </row>
     <row r="186" spans="1:8">
@@ -7048,19 +7030,19 @@
         <v>226</v>
       </c>
       <c r="D186" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E186" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F186" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G186" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="H186" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
     </row>
     <row r="187" spans="1:8">
@@ -7074,19 +7056,19 @@
         <v>227</v>
       </c>
       <c r="D187" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="E187" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F187" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G187" t="s">
-        <v>549</v>
+        <v>536</v>
       </c>
       <c r="H187" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="188" spans="1:8">
@@ -7100,19 +7082,19 @@
         <v>228</v>
       </c>
       <c r="D188" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="E188" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F188" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G188" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="H188" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="189" spans="1:8">
@@ -7126,19 +7108,19 @@
         <v>229</v>
       </c>
       <c r="D189" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="E189" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F189" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G189" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H189" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="190" spans="1:8">
@@ -7152,45 +7134,45 @@
         <v>230</v>
       </c>
       <c r="D190" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="E190" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F190" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G190" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="H190" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="191" spans="1:8">
       <c r="A191" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B191" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C191" t="s">
         <v>231</v>
       </c>
       <c r="D191" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="E191" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F191" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="G191" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="H191" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="192" spans="1:8">
@@ -7204,71 +7186,71 @@
         <v>232</v>
       </c>
       <c r="D192" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="E192" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F192" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G192" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="H192" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
     </row>
     <row r="193" spans="1:8">
       <c r="A193" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B193" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C193" t="s">
         <v>233</v>
       </c>
       <c r="D193" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="E193" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F193" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="G193" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="H193" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
     </row>
     <row r="194" spans="1:8">
       <c r="A194" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B194" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C194" t="s">
         <v>234</v>
       </c>
       <c r="D194" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E194" t="s">
+        <v>520</v>
+      </c>
+      <c r="F194" t="s">
         <v>526</v>
       </c>
-      <c r="F194" t="s">
-        <v>531</v>
-      </c>
       <c r="G194" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="H194" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="195" spans="1:8">
@@ -7282,19 +7264,19 @@
         <v>235</v>
       </c>
       <c r="D195" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="E195" t="s">
+        <v>520</v>
+      </c>
+      <c r="F195" t="s">
         <v>526</v>
       </c>
-      <c r="F195" t="s">
-        <v>532</v>
-      </c>
       <c r="G195" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="H195" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
     </row>
     <row r="196" spans="1:8">
@@ -7308,19 +7290,19 @@
         <v>236</v>
       </c>
       <c r="D196" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="E196" t="s">
+        <v>520</v>
+      </c>
+      <c r="F196" t="s">
         <v>526</v>
       </c>
-      <c r="F196" t="s">
-        <v>532</v>
-      </c>
       <c r="G196" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="H196" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="197" spans="1:8">
@@ -7334,19 +7316,19 @@
         <v>237</v>
       </c>
       <c r="D197" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E197" t="s">
+        <v>520</v>
+      </c>
+      <c r="F197" t="s">
         <v>526</v>
       </c>
-      <c r="F197" t="s">
-        <v>532</v>
-      </c>
       <c r="G197" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="H197" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
     </row>
     <row r="198" spans="1:8">
@@ -7360,19 +7342,19 @@
         <v>238</v>
       </c>
       <c r="D198" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="E198" t="s">
+        <v>520</v>
+      </c>
+      <c r="F198" t="s">
         <v>526</v>
       </c>
-      <c r="F198" t="s">
-        <v>532</v>
-      </c>
       <c r="G198" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="H198" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
     </row>
     <row r="199" spans="1:8">
@@ -7386,71 +7368,71 @@
         <v>239</v>
       </c>
       <c r="D199" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="E199" t="s">
+        <v>520</v>
+      </c>
+      <c r="F199" t="s">
         <v>526</v>
       </c>
-      <c r="F199" t="s">
-        <v>532</v>
-      </c>
       <c r="G199" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H199" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
     </row>
     <row r="200" spans="1:8">
       <c r="A200" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B200" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C200" t="s">
         <v>240</v>
       </c>
       <c r="D200" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="E200" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F200" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="G200" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="H200" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
     </row>
     <row r="201" spans="1:8">
       <c r="A201" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B201" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C201" t="s">
         <v>241</v>
       </c>
       <c r="D201" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E201" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F201" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="G201" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="H201" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
     </row>
     <row r="202" spans="1:8">
@@ -7464,19 +7446,19 @@
         <v>242</v>
       </c>
       <c r="D202" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="E202" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F202" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G202" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="H202" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="203" spans="1:8">
@@ -7490,19 +7472,19 @@
         <v>243</v>
       </c>
       <c r="D203" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="E203" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F203" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G203" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="H203" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="204" spans="1:8">
@@ -7516,19 +7498,19 @@
         <v>244</v>
       </c>
       <c r="D204" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="E204" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F204" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G204" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="H204" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
     </row>
     <row r="205" spans="1:8">
@@ -7542,97 +7524,97 @@
         <v>245</v>
       </c>
       <c r="D205" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="E205" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F205" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G205" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="H205" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
     </row>
     <row r="206" spans="1:8">
       <c r="A206" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B206" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C206" t="s">
         <v>246</v>
       </c>
       <c r="D206" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="E206" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F206" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="G206" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H206" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
     </row>
     <row r="207" spans="1:8">
       <c r="A207" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B207" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C207" t="s">
         <v>247</v>
       </c>
       <c r="D207" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="E207" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F207" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="G207" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H207" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
     </row>
     <row r="208" spans="1:8">
       <c r="A208" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B208" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C208" t="s">
         <v>248</v>
       </c>
       <c r="D208" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="E208" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="F208" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G208" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="H208" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="209" spans="1:8">
@@ -7646,357 +7628,357 @@
         <v>249</v>
       </c>
       <c r="D209" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="E209" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F209" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="G209" t="s">
         <v>547</v>
       </c>
       <c r="H209" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="210" spans="1:8">
       <c r="A210" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B210" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C210" t="s">
         <v>250</v>
       </c>
       <c r="D210" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="E210" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F210" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="G210" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="H210" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="211" spans="1:8">
       <c r="A211" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B211" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C211" t="s">
         <v>251</v>
       </c>
       <c r="D211" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="E211" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F211" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="G211" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="H211" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
     </row>
     <row r="212" spans="1:8">
       <c r="A212" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B212" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C212" t="s">
         <v>252</v>
       </c>
       <c r="D212" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="E212" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="F212" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="G212" t="s">
-        <v>551</v>
+        <v>522</v>
       </c>
       <c r="H212" t="s">
-        <v>599</v>
+        <v>532</v>
       </c>
     </row>
     <row r="213" spans="1:8">
       <c r="A213" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B213" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C213" t="s">
         <v>253</v>
       </c>
       <c r="D213" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E213" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="F213" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="G213" t="s">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="H213" t="s">
-        <v>572</v>
+        <v>533</v>
       </c>
     </row>
     <row r="214" spans="1:8">
       <c r="A214" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B214" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C214" t="s">
         <v>254</v>
       </c>
       <c r="D214" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E214" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="F214" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="G214" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="H214" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
     </row>
     <row r="215" spans="1:8">
       <c r="A215" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B215" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C215" t="s">
         <v>255</v>
       </c>
       <c r="D215" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="E215" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="F215" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="G215" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="H215" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="216" spans="1:8">
       <c r="A216" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B216" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C216" t="s">
         <v>256</v>
       </c>
       <c r="D216" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="E216" t="s">
+        <v>520</v>
+      </c>
+      <c r="F216" t="s">
         <v>528</v>
       </c>
-      <c r="F216" t="s">
-        <v>538</v>
-      </c>
       <c r="G216" t="s">
-        <v>528</v>
+        <v>541</v>
       </c>
       <c r="H216" t="s">
-        <v>538</v>
+        <v>613</v>
       </c>
     </row>
     <row r="217" spans="1:8">
       <c r="A217" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B217" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C217" t="s">
         <v>257</v>
       </c>
       <c r="D217" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="E217" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="F217" t="s">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="G217" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H217" t="s">
-        <v>539</v>
+        <v>597</v>
       </c>
     </row>
     <row r="218" spans="1:8">
       <c r="A218" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B218" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C218" t="s">
         <v>258</v>
       </c>
       <c r="D218" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="E218" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="F218" t="s">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="G218" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="H218" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
     </row>
     <row r="219" spans="1:8">
       <c r="A219" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B219" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C219" t="s">
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="E219" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="F219" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="G219" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="H219" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
     </row>
     <row r="220" spans="1:8">
       <c r="A220" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B220" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C220" t="s">
         <v>260</v>
       </c>
       <c r="D220" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="E220" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F220" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="G220" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H220" t="s">
-        <v>619</v>
+        <v>600</v>
       </c>
     </row>
     <row r="221" spans="1:8">
       <c r="A221" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B221" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C221" t="s">
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="E221" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F221" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="G221" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="H221" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="222" spans="1:8">
       <c r="A222" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B222" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C222" t="s">
         <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="E222" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F222" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="G222" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="H222" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="223" spans="1:8">
@@ -8010,149 +7992,149 @@
         <v>263</v>
       </c>
       <c r="D223" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E223" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F223" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="G223" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="H223" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="224" spans="1:8">
       <c r="A224" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B224" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C224" t="s">
         <v>264</v>
       </c>
       <c r="D224" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="E224" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F224" t="s">
-        <v>542</v>
+        <v>524</v>
       </c>
       <c r="G224" t="s">
-        <v>556</v>
+        <v>539</v>
       </c>
       <c r="H224" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="225" spans="1:8">
       <c r="A225" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B225" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C225" t="s">
         <v>265</v>
       </c>
       <c r="D225" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E225" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F225" t="s">
-        <v>542</v>
+        <v>528</v>
       </c>
       <c r="G225" t="s">
-        <v>556</v>
+        <v>541</v>
       </c>
       <c r="H225" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="226" spans="1:8">
       <c r="A226" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B226" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C226" t="s">
         <v>266</v>
       </c>
       <c r="D226" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="E226" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F226" t="s">
-        <v>542</v>
+        <v>528</v>
       </c>
       <c r="G226" t="s">
-        <v>556</v>
+        <v>541</v>
       </c>
       <c r="H226" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="227" spans="1:8">
       <c r="A227" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B227" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C227" t="s">
         <v>267</v>
       </c>
       <c r="D227" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E227" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F227" t="s">
-        <v>542</v>
+        <v>528</v>
       </c>
       <c r="G227" t="s">
-        <v>556</v>
+        <v>541</v>
       </c>
       <c r="H227" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="228" spans="1:8">
       <c r="A228" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B228" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C228" t="s">
         <v>268</v>
       </c>
       <c r="D228" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="E228" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F228" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="G228" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="H228" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="229" spans="1:8">
@@ -8166,97 +8148,97 @@
         <v>269</v>
       </c>
       <c r="D229" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E229" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F229" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="G229" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H229" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
     </row>
     <row r="230" spans="1:8">
       <c r="A230" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B230" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C230" t="s">
         <v>270</v>
       </c>
       <c r="D230" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="E230" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F230" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="G230" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="H230" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
     </row>
     <row r="231" spans="1:8">
       <c r="A231" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B231" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C231" t="s">
         <v>271</v>
       </c>
       <c r="D231" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="E231" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F231" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="G231" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="H231" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
     </row>
     <row r="232" spans="1:8">
       <c r="A232" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B232" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C232" t="s">
         <v>272</v>
       </c>
       <c r="D232" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E232" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F232" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="G232" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="H232" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="233" spans="1:8">
@@ -8270,71 +8252,71 @@
         <v>273</v>
       </c>
       <c r="D233" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E233" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F233" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G233" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="H233" t="s">
-        <v>613</v>
+        <v>570</v>
       </c>
     </row>
     <row r="234" spans="1:8">
       <c r="A234" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B234" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C234" t="s">
         <v>274</v>
       </c>
       <c r="D234" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="E234" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F234" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="G234" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="H234" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
     </row>
     <row r="235" spans="1:8">
       <c r="A235" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B235" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C235" t="s">
         <v>275</v>
       </c>
       <c r="D235" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E235" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F235" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="G235" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="H235" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="236" spans="1:8">
@@ -8348,192 +8330,114 @@
         <v>276</v>
       </c>
       <c r="D236" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="E236" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F236" t="s">
-        <v>530</v>
-      </c>
-      <c r="G236" t="s">
-        <v>557</v>
+        <v>524</v>
       </c>
       <c r="H236" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
     </row>
     <row r="237" spans="1:8">
       <c r="A237" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B237" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C237" t="s">
         <v>277</v>
       </c>
       <c r="D237" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="E237" t="s">
+        <v>520</v>
+      </c>
+      <c r="F237" t="s">
         <v>526</v>
       </c>
-      <c r="F237" t="s">
-        <v>533</v>
-      </c>
       <c r="G237" t="s">
-        <v>557</v>
-      </c>
-      <c r="H237" t="s">
-        <v>616</v>
+        <v>539</v>
       </c>
     </row>
     <row r="238" spans="1:8">
       <c r="A238" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B238" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C238" t="s">
         <v>278</v>
       </c>
       <c r="D238" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="E238" t="s">
-        <v>526</v>
-      </c>
-      <c r="F238" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
       <c r="G238" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="H238" t="s">
-        <v>617</v>
+        <v>530</v>
       </c>
     </row>
     <row r="239" spans="1:8">
       <c r="A239" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B239" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C239" t="s">
         <v>279</v>
       </c>
       <c r="D239" t="s">
+        <v>518</v>
+      </c>
+      <c r="E239" t="s">
         <v>521</v>
       </c>
-      <c r="E239" t="s">
-        <v>526</v>
-      </c>
       <c r="F239" t="s">
-        <v>530</v>
+        <v>525</v>
+      </c>
+      <c r="G239" t="s">
+        <v>539</v>
       </c>
       <c r="H239" t="s">
-        <v>569</v>
+        <v>588</v>
       </c>
     </row>
     <row r="240" spans="1:8">
       <c r="A240" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="B240" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="C240" t="s">
         <v>280</v>
       </c>
       <c r="D240" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="E240" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="F240" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="G240" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="241" spans="1:8">
-      <c r="A241" t="s">
-        <v>22</v>
-      </c>
-      <c r="B241" t="s">
-        <v>39</v>
-      </c>
-      <c r="C241" t="s">
-        <v>281</v>
-      </c>
-      <c r="D241" t="s">
-        <v>523</v>
-      </c>
-      <c r="E241" t="s">
-        <v>527</v>
-      </c>
-      <c r="G241" t="s">
-        <v>551</v>
-      </c>
-      <c r="H241" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="242" spans="1:8">
-      <c r="A242" t="s">
-        <v>23</v>
-      </c>
-      <c r="B242" t="s">
-        <v>40</v>
-      </c>
-      <c r="C242" t="s">
-        <v>282</v>
-      </c>
-      <c r="D242" t="s">
-        <v>524</v>
-      </c>
-      <c r="E242" t="s">
-        <v>527</v>
-      </c>
-      <c r="F242" t="s">
-        <v>531</v>
-      </c>
-      <c r="G242" t="s">
-        <v>545</v>
-      </c>
-      <c r="H242" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="243" spans="1:8">
-      <c r="A243" t="s">
-        <v>24</v>
-      </c>
-      <c r="B243" t="s">
-        <v>41</v>
-      </c>
-      <c r="C243" t="s">
-        <v>283</v>
-      </c>
-      <c r="D243" t="s">
-        <v>525</v>
-      </c>
-      <c r="E243" t="s">
-        <v>527</v>
-      </c>
-      <c r="F243" t="s">
-        <v>534</v>
-      </c>
-      <c r="G243" t="s">
-        <v>547</v>
-      </c>
-      <c r="H243" t="s">
-        <v>612</v>
+        <v>541</v>
+      </c>
+      <c r="H240" t="s">
+        <v>606</v>
       </c>
     </row>
   </sheetData>
@@ -8554,62 +8458,62 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B2" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="C2" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B3" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C3" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B4" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="C4" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B5" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="C5" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B6" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="C6" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
     </row>
   </sheetData>
